--- a/rcads/data/xls/31_ResponseOptions.xlsx
+++ b/rcads/data/xls/31_ResponseOptions.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_31_ResponseOptions"/>
   </sheets>
   <definedNames>
-    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$150</definedName>
+    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$158</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2752,6 +2752,134 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="151">
+      <c r="A151" s="0">
+        <v>152</v>
+      </c>
+      <c r="B151" s="0">
+        <v>1</v>
+      </c>
+      <c r="C151" s="0">
+        <v>36</v>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="152">
+      <c r="A152" s="0">
+        <v>153</v>
+      </c>
+      <c r="B152" s="0">
+        <v>2</v>
+      </c>
+      <c r="C152" s="0">
+        <v>36</v>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="153">
+      <c r="A153" s="0">
+        <v>154</v>
+      </c>
+      <c r="B153" s="0">
+        <v>3</v>
+      </c>
+      <c r="C153" s="0">
+        <v>36</v>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="154">
+      <c r="A154" s="0">
+        <v>155</v>
+      </c>
+      <c r="B154" s="0">
+        <v>4</v>
+      </c>
+      <c r="C154" s="0">
+        <v>36</v>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="155">
+      <c r="A155" s="0">
+        <v>156</v>
+      </c>
+      <c r="B155" s="0">
+        <v>1</v>
+      </c>
+      <c r="C155" s="0">
+        <v>41</v>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t>Angilokothi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="156">
+      <c r="A156" s="0">
+        <v>157</v>
+      </c>
+      <c r="B156" s="0">
+        <v>2</v>
+      </c>
+      <c r="C156" s="0">
+        <v>41</v>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t>Ngezinye izikhathi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="157">
+      <c r="A157" s="0">
+        <v>158</v>
+      </c>
+      <c r="B157" s="0">
+        <v>3</v>
+      </c>
+      <c r="C157" s="0">
+        <v>41</v>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t>Ngokuvamile</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="158">
+      <c r="A158" s="0">
+        <v>159</v>
+      </c>
+      <c r="B158" s="0">
+        <v>4</v>
+      </c>
+      <c r="C158" s="0">
+        <v>41</v>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t>Njalo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rcads/data/xls/31_ResponseOptions.xlsx
+++ b/rcads/data/xls/31_ResponseOptions.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_31_ResponseOptions"/>
   </sheets>
   <definedNames>
-    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$158</definedName>
+    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$167</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2880,6 +2880,151 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="159">
+      <c r="A159" s="0">
+        <v>160</v>
+      </c>
+      <c r="B159" s="0">
+        <v>1</v>
+      </c>
+      <c r="C159" s="0">
+        <v>34</v>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t>Palibe</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="160">
+      <c r="A160" s="0">
+        <v>161</v>
+      </c>
+      <c r="B160" s="0">
+        <v>2</v>
+      </c>
+      <c r="C160" s="0">
+        <v>34</v>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t>Nthawi zina</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="161">
+      <c r="A161" s="0">
+        <v>162</v>
+      </c>
+      <c r="B161" s="0">
+        <v>3</v>
+      </c>
+      <c r="C161" s="0">
+        <v>34</v>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t>Nthawi zambiri</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="162">
+      <c r="A162" s="0">
+        <v>163</v>
+      </c>
+      <c r="B162" s="0">
+        <v>4</v>
+      </c>
+      <c r="C162" s="0">
+        <v>34</v>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>Nthawi zonse</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="163">
+      <c r="A163" s="0">
+        <v>164</v>
+      </c>
+      <c r="B163" s="0">
+        <v>3</v>
+      </c>
+      <c r="C163" s="0">
+        <v>34</v>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t>Kawiri kawiri</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="164">
+      <c r="A164" s="0">
+        <v>165</v>
+      </c>
+      <c r="B164" s="0">
+        <v>1</v>
+      </c>
+      <c r="C164" s="0">
+        <v>29</v>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t>কখনই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="165">
+      <c r="A165" s="0">
+        <v>166</v>
+      </c>
+      <c r="B165" s="0">
+        <v>2</v>
+      </c>
+      <c r="C165" s="0">
+        <v>29</v>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t>মাঝে_x000d_
+মাঝে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="166">
+      <c r="A166" s="0">
+        <v>167</v>
+      </c>
+      <c r="B166" s="0">
+        <v>3</v>
+      </c>
+      <c r="C166" s="0">
+        <v>29</v>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t>প্রায়ই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="167">
+      <c r="A167" s="0">
+        <v>168</v>
+      </c>
+      <c r="B167" s="0">
+        <v>4</v>
+      </c>
+      <c r="C167" s="0">
+        <v>29</v>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t>সবসময়</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
